--- a/temporary_files/logit_highu_base.xlsx
+++ b/temporary_files/logit_highu_base.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t xml:space="preserve">term</t>
   </si>
@@ -32,6 +32,9 @@
     <t xml:space="preserve">(Intercept)</t>
   </si>
   <si>
+    <t xml:space="preserve">reg_focus_dummy</t>
+  </si>
+  <si>
     <t xml:space="preserve">age</t>
   </si>
   <si>
@@ -50,9 +53,6 @@
     <t xml:space="preserve">previous_experience</t>
   </si>
   <si>
-    <t xml:space="preserve">regulatory_focusPrevention</t>
-  </si>
-  <si>
     <t xml:space="preserve">platform_preferenceAppStore</t>
   </si>
   <si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t xml:space="preserve">apporder_purchased4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">highU_exploredTRUE</t>
   </si>
 </sst>
 </file>
@@ -428,13 +425,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.88</v>
+        <v>-4.27</v>
       </c>
       <c r="C2" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.39</v>
+        <v>-4.02</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -445,16 +442,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01</v>
+        <v>0.07</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="D3" t="n">
-        <v>0.82</v>
+        <v>0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>0.41</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
@@ -462,16 +459,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>0.73</v>
+        <v>0.01</v>
       </c>
       <c r="C4" t="n">
-        <v>0.28</v>
+        <v>0.01</v>
       </c>
       <c r="D4" t="n">
-        <v>2.64</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="5">
@@ -479,16 +476,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.01</v>
+        <v>0.69</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09</v>
+        <v>0.27</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08</v>
+        <v>2.53</v>
       </c>
       <c r="E5" t="n">
-        <v>0.93</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="6">
@@ -496,16 +493,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>0.49</v>
+        <v>-0.01</v>
       </c>
       <c r="C6" t="n">
-        <v>0.23</v>
+        <v>0.08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.13</v>
+        <v>-0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="7">
@@ -513,16 +510,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>0.16</v>
+        <v>0.48</v>
       </c>
       <c r="C7" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3</v>
+        <v>2.09</v>
       </c>
       <c r="E7" t="n">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="8">
@@ -530,16 +527,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="C8" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="D8" t="n">
-        <v>0.47</v>
+        <v>1.29</v>
       </c>
       <c r="E8" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -547,16 +544,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="C9" t="n">
-        <v>0.27</v>
+        <v>0.11</v>
       </c>
       <c r="D9" t="n">
-        <v>0.12</v>
+        <v>0.52</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="10">
@@ -564,16 +561,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.21</v>
+        <v>-0.31</v>
       </c>
       <c r="C10" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.77</v>
+        <v>-1.15</v>
       </c>
       <c r="E10" t="n">
-        <v>0.44</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11">
@@ -581,16 +578,16 @@
         <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.35</v>
+        <v>-0.36</v>
       </c>
       <c r="C11" t="n">
         <v>0.3</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.15</v>
+        <v>-1.18</v>
       </c>
       <c r="E11" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="12">
@@ -598,16 +595,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="C12" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="D12" t="n">
-        <v>0.88</v>
+        <v>0.68</v>
       </c>
       <c r="E12" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
@@ -615,16 +612,16 @@
         <v>16</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="C13" t="n">
         <v>0.36</v>
       </c>
       <c r="D13" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="E13" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="14">
@@ -632,16 +629,16 @@
         <v>17</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.09</v>
+        <v>-0.18</v>
       </c>
       <c r="C14" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.22</v>
+        <v>-0.44</v>
       </c>
       <c r="E14" t="n">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="15">
@@ -649,16 +646,16 @@
         <v>18</v>
       </c>
       <c r="B15" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="D15" t="n">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="16">
@@ -666,16 +663,16 @@
         <v>19</v>
       </c>
       <c r="B16" t="n">
-        <v>0.11</v>
+        <v>0.07</v>
       </c>
       <c r="C16" t="n">
         <v>0.39</v>
       </c>
       <c r="D16" t="n">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
       <c r="E16" t="n">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="17">
@@ -683,33 +680,16 @@
         <v>20</v>
       </c>
       <c r="B17" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="C17" t="n">
         <v>0.39</v>
       </c>
       <c r="D17" t="n">
-        <v>0.27</v>
+        <v>0.16</v>
       </c>
       <c r="E17" t="n">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.01</v>
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
